--- a/6.Gerenciamento de Projeto/BRA - Planejamento e Controle do Projeto.xlsx
+++ b/6.Gerenciamento de Projeto/BRA - Planejamento e Controle do Projeto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fabioas\Development\bra-brasileirao_analyst\6.Gerenciamento de Projeto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDB9E48-34D9-4AE1-A170-D0BEA21990C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD62EC7-822C-4E82-B7EA-EA45F2412BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{31237A52-FFD1-4E1D-B5BB-391D11929C61}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="1" activeTab="1" xr2:uid="{31237A52-FFD1-4E1D-B5BB-391D11929C61}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipe" sheetId="1" r:id="rId1"/>
@@ -4738,7 +4738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="251">
   <si>
     <t>Equipe</t>
   </si>
@@ -5464,9 +5464,6 @@
     <t>Fazer login</t>
   </si>
   <si>
-    <t>Favoritar atleta</t>
-  </si>
-  <si>
     <t>Comparar clubes</t>
   </si>
   <si>
@@ -5610,66 +5607,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Projetar testes para </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>UC 06 - Comparar clubes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Modelar, Implementar e Testar o </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>UC 06 - Comparar clubes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Projetar testes para </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>UC 05 - Favoritar atleta</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Modelar, Implementar e Testar o </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>UC 05 - Favoritar atleta</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Modelar, Implementar e Testar o </t>
     </r>
     <r>
@@ -5747,12 +5684,6 @@
     <t>Histórias de Usuário, Modelo de Objetos, Modelo de Arquitetura, UC 03</t>
   </si>
   <si>
-    <t>UC 04 e UC 06</t>
-  </si>
-  <si>
-    <t>UC 05, UC 01 e UC 02, Guia de Implantação, Modelo de Implantação, Manual de Suporte e Treinamento e sistema em produção</t>
-  </si>
-  <si>
     <t>Entregue</t>
   </si>
   <si>
@@ -5772,6 +5703,45 @@
   </si>
   <si>
     <t>Ver estatísticas dos atletas</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Projetar testes para </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>UC 05 - Comparar clubes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Modelar, Implementar e Testar o </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>UC 05 - Comparar clubes</t>
+    </r>
+  </si>
+  <si>
+    <t>UC 04 e UC 05</t>
+  </si>
+  <si>
+    <t>UC 01 e UC 02, Guia de Implantação, Modelo de Implantação, Manual de Suporte e Treinamento e sistema em produção</t>
+  </si>
+  <si>
+    <t>Release-1.1.0</t>
   </si>
 </sst>
 </file>
@@ -6176,7 +6146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -6298,6 +6268,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -6322,7 +6301,7 @@
     <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="10" applyProtection="1"/>
     <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6375,10 +6354,6 @@
     </xf>
     <xf numFmtId="164" fontId="18" fillId="8" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6705,17 +6680,24 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="5" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="10" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6724,45 +6706,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="5" borderId="7" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="14" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="25" fillId="5" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="10" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="29" fillId="15" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6778,6 +6738,21 @@
     <xf numFmtId="164" fontId="29" fillId="15" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6807,6 +6782,32 @@
     </xf>
     <xf numFmtId="164" fontId="27" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="11" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="11" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="17">
@@ -6912,10 +6913,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>314080</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>163838</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1660</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>2548</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3725997" cy="1047957"/>
     <xdr:pic>
@@ -6943,7 +6944,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7641980" y="2716538"/>
+          <a:off x="7647060" y="2364748"/>
           <a:ext cx="3725997" cy="1047957"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8705,18 +8706,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
     </row>
     <row r="2" spans="1:3" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="135" t="s">
-        <v>219</v>
-      </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
+      <c r="A2" s="136" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
     </row>
     <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -8734,10 +8735,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="115" t="s">
-        <v>220</v>
+        <v>222</v>
+      </c>
+      <c r="C4" s="114" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -8745,10 +8746,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C5" s="115" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="C5" s="114" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -8756,10 +8757,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="115" t="s">
-        <v>222</v>
+        <v>224</v>
+      </c>
+      <c r="C6" s="114" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -8836,13 +8837,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F6C5642-BF97-4AFF-B370-04CC3D024494}">
-  <dimension ref="A1:AMJ49"/>
+  <dimension ref="A1:AMJ47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.19921875" style="21" customWidth="1"/>
+    <col min="1" max="1" width="10.19921875" style="20" customWidth="1"/>
     <col min="2" max="2" width="11.59765625" style="4" customWidth="1"/>
     <col min="3" max="3" width="64.19921875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="8.69921875" style="19" customWidth="1"/>
+    <col min="4" max="4" width="8.69921875" style="18" customWidth="1"/>
     <col min="5" max="5" width="1.59765625" style="4" customWidth="1"/>
     <col min="6" max="6" width="4.19921875" style="4" customWidth="1"/>
     <col min="7" max="7" width="26.3984375" style="4" bestFit="1" customWidth="1"/>
@@ -8854,38 +8855,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="F1" s="138" t="s">
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="F1" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
     </row>
     <row r="2" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="139" t="s">
+      <c r="A2" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="F2" s="140" t="s">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="F2" s="133" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="140"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -8906,20 +8907,20 @@
       <c r="G3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="141" t="s">
+      <c r="H3" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="134"/>
     </row>
     <row r="4" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="136" t="s">
+      <c r="A4" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="136"/>
-      <c r="C4" s="136"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
       <c r="D4" s="8" t="s">
         <v>17</v>
       </c>
@@ -9034,7 +9035,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H7" s="15">
         <v>8</v>
@@ -9070,7 +9071,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="H8" s="15">
         <v>10</v>
@@ -9102,27 +9103,27 @@
       <c r="D9" s="13">
         <v>0.5</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="14">
         <v>5</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="164" t="s">
         <v>212</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="165">
+        <v>9</v>
+      </c>
+      <c r="I9" s="165">
+        <v>6</v>
+      </c>
+      <c r="J9" s="165">
+        <v>0</v>
+      </c>
+      <c r="K9" s="165">
         <v>7</v>
       </c>
-      <c r="I9" s="15">
-        <v>3</v>
-      </c>
-      <c r="J9" s="15">
-        <v>0</v>
-      </c>
-      <c r="K9" s="15">
-        <v>4</v>
-      </c>
-      <c r="L9" s="16">
+      <c r="L9" s="166">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="13.8" x14ac:dyDescent="0.25">
@@ -9138,35 +9139,20 @@
       <c r="D10" s="13">
         <v>1</v>
       </c>
-      <c r="F10" s="17">
-        <v>6</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="H10" s="15">
-        <v>9</v>
-      </c>
-      <c r="I10" s="15">
-        <v>6</v>
-      </c>
-      <c r="J10" s="15">
-        <v>0</v>
-      </c>
-      <c r="K10" s="15">
-        <v>7</v>
-      </c>
-      <c r="L10" s="16">
-        <f t="shared" ref="L10" si="1">SUM(H10:K10)</f>
-        <v>22</v>
-      </c>
+      <c r="F10" s="167"/>
+      <c r="G10" s="168"/>
+      <c r="H10" s="169"/>
+      <c r="I10" s="169"/>
+      <c r="J10" s="169"/>
+      <c r="K10" s="169"/>
+      <c r="L10" s="170"/>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="136" t="s">
+      <c r="A11" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="136"/>
-      <c r="C11" s="136"/>
+      <c r="B11" s="129"/>
+      <c r="C11" s="129"/>
       <c r="D11" s="8">
         <f>SUM(D5:D10)</f>
         <v>10.5</v>
@@ -9208,7 +9194,7 @@
         <v>30</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D13" s="13">
         <v>5</v>
@@ -9229,7 +9215,7 @@
         <v>30</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D14" s="13">
         <v>2</v>
@@ -9250,7 +9236,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D15" s="13">
         <v>8</v>
@@ -9271,7 +9257,7 @@
         <v>30</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D16" s="13">
         <v>0.5</v>
@@ -9292,7 +9278,7 @@
         <v>30</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D17" s="13">
         <v>1</v>
@@ -9312,7 +9298,7 @@
       <c r="B18" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="17" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="13">
@@ -9334,16 +9320,16 @@
         <v>30</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D19" s="13">
         <v>8</v>
       </c>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
@@ -9353,16 +9339,16 @@
         <v>30</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D20" s="13">
         <v>2</v>
       </c>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
@@ -9371,17 +9357,17 @@
       <c r="B21" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>235</v>
+      <c r="C21" s="17" t="s">
+        <v>234</v>
       </c>
       <c r="D21" s="13">
         <v>1</v>
       </c>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
@@ -9390,17 +9376,17 @@
       <c r="B22" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>33</v>
       </c>
       <c r="D22" s="13">
         <v>0.5</v>
       </c>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
     </row>
     <row r="23" spans="1:12" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
@@ -9409,7 +9395,7 @@
       <c r="B23" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="17" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="13">
@@ -9449,7 +9435,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D26" s="13">
         <v>1</v>
@@ -9463,7 +9449,7 @@
         <v>35</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D27" s="13">
         <v>20</v>
@@ -9477,7 +9463,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D28" s="13">
         <v>1</v>
@@ -9491,7 +9477,7 @@
         <v>35</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D29" s="13">
         <v>20</v>
@@ -9499,27 +9485,27 @@
     </row>
     <row r="30" spans="1:12" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="D30" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="D31" s="13">
         <v>8</v>
@@ -9527,13 +9513,13 @@
     </row>
     <row r="32" spans="1:12" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="D32" s="13">
         <v>2</v>
@@ -9547,88 +9533,88 @@
         <v>35</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="D33" s="13">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>242</v>
+      <c r="C34" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="D34" s="13">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>241</v>
+      <c r="C35" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="D35" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A36" s="10">
-        <v>29</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D36" s="13">
-        <v>0.5</v>
+      <c r="A36" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="8">
+        <f>SUM(D25:D35)</f>
+        <v>61.5</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="D37" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="10">
+        <v>32</v>
+      </c>
+      <c r="B38" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8">
-        <f>SUM(D25:D37)</f>
-        <v>70.5</v>
+      <c r="C38" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="13">
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>31</v>
+      <c r="C39" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="D39" s="13">
         <v>1</v>
@@ -9636,41 +9622,41 @@
     </row>
     <row r="40" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="18" t="s">
-        <v>37</v>
+      <c r="C40" s="17" t="s">
+        <v>39</v>
       </c>
       <c r="D40" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="18" t="s">
-        <v>38</v>
+      <c r="C41" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="D41" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="18" t="s">
-        <v>39</v>
+      <c r="C42" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="D42" s="13">
         <v>3</v>
@@ -9678,87 +9664,59 @@
     </row>
     <row r="43" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>36</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>218</v>
+        <v>41</v>
       </c>
       <c r="D43" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>36</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D44" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
-        <v>37</v>
-      </c>
-      <c r="B45" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>41</v>
+      <c r="C45" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="D45" s="13">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A46" s="10">
-        <v>38</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D46" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A47" s="10">
-        <v>39</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D47" s="13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A48" s="23"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="8">
-        <f>SUM(D39:D47)</f>
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="8">
+        <f>SUM(D37:D45)</f>
         <v>18.5</v>
       </c>
     </row>
-    <row r="49" spans="4:4" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="D49" s="22">
-        <f>SUM(D11,D24,D38,D48)</f>
-        <v>130</v>
+    <row r="47" spans="1:4" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="D47" s="21">
+        <f>SUM(D11,D24,D36,D46)</f>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -9785,47 +9743,47 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="24" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="23" customWidth="1"/>
     <col min="3" max="3" width="20.69921875" style="1" customWidth="1"/>
     <col min="4" max="1024" width="8.09765625" style="1" customWidth="1"/>
     <col min="1025" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="137" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
     </row>
     <row r="2" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="143" t="s">
+      <c r="A3" s="138" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="143"/>
-      <c r="C3" s="143"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="138"/>
     </row>
     <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="26">
-        <f>Backlog_Produto!$D$49</f>
-        <v>130</v>
-      </c>
-      <c r="C4" s="25" t="s">
+      <c r="B4" s="25">
+        <f>Backlog_Produto!$D$47</f>
+        <v>121</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>0.6</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="26" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -9833,168 +9791,168 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>3</v>
       </c>
-      <c r="C6" s="29"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>8</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="30">
         <f>B6*B7*2</f>
         <v>48</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="32">
         <f>B11/2</f>
-        <v>4.333333333333333</v>
-      </c>
-      <c r="C9" s="32" t="s">
+        <v>4.0333333333333332</v>
+      </c>
+      <c r="C9" s="31" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="32">
         <f>B4+(B4*B5)</f>
-        <v>208</v>
-      </c>
-      <c r="C10" s="34" t="s">
+        <v>193.6</v>
+      </c>
+      <c r="C10" s="33" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <f>B10/B8*2</f>
-        <v>8.6666666666666661</v>
-      </c>
-      <c r="C11" s="29" t="s">
+        <v>8.0666666666666664</v>
+      </c>
+      <c r="C11" s="28" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="34">
         <f>B11/4</f>
-        <v>2.1666666666666665</v>
-      </c>
-      <c r="C12" s="25" t="s">
+        <v>2.0166666666666666</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="143" t="s">
+      <c r="A14" s="138" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="143"/>
-      <c r="C14" s="143"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="35">
         <v>15</v>
       </c>
-      <c r="C15" s="37"/>
+      <c r="C15" s="36"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="37">
         <f>B10*B15</f>
-        <v>3120</v>
-      </c>
-      <c r="C16" s="37"/>
+        <v>2904</v>
+      </c>
+      <c r="C16" s="36"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="27">
         <v>0.2</v>
       </c>
-      <c r="C17" s="37"/>
+      <c r="C17" s="36"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="39">
+      <c r="B18" s="38">
         <f>B16*B17</f>
-        <v>624</v>
-      </c>
-      <c r="C18" s="37"/>
+        <v>580.80000000000007</v>
+      </c>
+      <c r="C18" s="36"/>
     </row>
     <row r="19" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="40">
         <f>B16+B18</f>
-        <v>3744</v>
-      </c>
-      <c r="C19" s="37"/>
+        <v>3484.8</v>
+      </c>
+      <c r="C19" s="36"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="27">
         <v>0.2</v>
       </c>
-      <c r="C20" s="37"/>
+      <c r="C20" s="36"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="41">
         <f>B19*B20</f>
-        <v>748.80000000000007</v>
-      </c>
-      <c r="C21" s="37"/>
+        <v>696.96</v>
+      </c>
+      <c r="C21" s="36"/>
     </row>
     <row r="22" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="41">
+      <c r="B22" s="40">
         <f>B19+B21</f>
-        <v>4492.8</v>
-      </c>
-      <c r="C22" s="37"/>
+        <v>4181.76</v>
+      </c>
+      <c r="C22" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -10014,328 +9972,338 @@
   <dimension ref="A1:AMJ16"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.09765625" style="59" customWidth="1"/>
+    <col min="1" max="1" width="6.09765625" style="58" customWidth="1"/>
     <col min="2" max="2" width="45.19921875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.8984375" style="59" customWidth="1"/>
+    <col min="3" max="3" width="13.8984375" style="58" customWidth="1"/>
     <col min="4" max="6" width="13.09765625" style="4" customWidth="1"/>
     <col min="7" max="9" width="13" style="4" customWidth="1"/>
-    <col min="10" max="10" width="13" style="21" customWidth="1"/>
+    <col min="10" max="10" width="13" style="20" customWidth="1"/>
     <col min="11" max="11" width="14.69921875" style="4" customWidth="1"/>
     <col min="12" max="1024" width="8.5" style="4" customWidth="1"/>
     <col min="1025" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
     </row>
     <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="140" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="43">
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="42">
         <f>Planejamento!$B$10</f>
-        <v>208</v>
-      </c>
-      <c r="F2" s="44"/>
-      <c r="G2" s="131" t="s">
+        <v>193.6</v>
+      </c>
+      <c r="F2" s="43"/>
+      <c r="G2" s="140" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="43"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="42"/>
     </row>
     <row r="3" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="132" t="s">
+      <c r="A3" s="44"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="133" t="s">
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="142" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="133"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="50"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="142"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="48" t="s">
+      <c r="H4" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="J4" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="K4" s="48" t="s">
+      <c r="K4" s="47" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="52">
+      <c r="A5" s="51">
         <v>1</v>
       </c>
-      <c r="B5" s="116" t="s">
-        <v>246</v>
-      </c>
-      <c r="C5" s="117">
+      <c r="B5" s="115" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="116">
         <v>46252</v>
       </c>
-      <c r="D5" s="117">
+      <c r="D5" s="116">
         <v>46266</v>
       </c>
-      <c r="E5" s="118">
+      <c r="E5" s="117">
         <v>10.5</v>
       </c>
-      <c r="F5" s="119" t="s">
+      <c r="F5" s="118" t="s">
+        <v>243</v>
+      </c>
+      <c r="G5" s="116">
+        <v>46252</v>
+      </c>
+      <c r="H5" s="116">
+        <v>46266</v>
+      </c>
+      <c r="I5" s="117">
+        <v>10.5</v>
+      </c>
+      <c r="J5" s="119">
+        <v>0</v>
+      </c>
+      <c r="K5" s="120" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="51">
+        <v>2</v>
+      </c>
+      <c r="B6" s="115" t="s">
+        <v>242</v>
+      </c>
+      <c r="C6" s="116">
+        <v>46273</v>
+      </c>
+      <c r="D6" s="116">
+        <v>46287</v>
+      </c>
+      <c r="E6" s="121">
+        <v>30.5</v>
+      </c>
+      <c r="F6" s="118" t="s">
+        <v>243</v>
+      </c>
+      <c r="G6" s="116">
+        <v>46266</v>
+      </c>
+      <c r="H6" s="116">
+        <v>46323</v>
+      </c>
+      <c r="I6" s="121">
+        <v>56</v>
+      </c>
+      <c r="J6" s="122">
+        <v>25</v>
+      </c>
+      <c r="K6" s="120" t="s">
         <v>250</v>
       </c>
-      <c r="G5" s="117">
-        <v>46252</v>
-      </c>
-      <c r="H5" s="117">
-        <v>46266</v>
-      </c>
-      <c r="I5" s="118">
-        <v>10.5</v>
-      </c>
-      <c r="J5" s="120">
-        <v>0</v>
-      </c>
-      <c r="K5" s="121" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="52">
-        <v>2</v>
-      </c>
-      <c r="B6" s="116" t="s">
-        <v>247</v>
-      </c>
-      <c r="C6" s="117">
-        <v>46273</v>
-      </c>
-      <c r="D6" s="117">
-        <v>46287</v>
-      </c>
-      <c r="E6" s="122">
-        <v>30.5</v>
-      </c>
-      <c r="F6" s="119" t="s">
+    </row>
+    <row r="7" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="51">
+        <v>3</v>
+      </c>
+      <c r="B7" s="115" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="116">
+        <v>46294</v>
+      </c>
+      <c r="D7" s="116">
+        <v>46308</v>
+      </c>
+      <c r="E7" s="121">
+        <v>43</v>
+      </c>
+      <c r="F7" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="121"/>
-    </row>
-    <row r="7" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="52">
-        <v>3</v>
-      </c>
-      <c r="B7" s="116" t="s">
-        <v>248</v>
-      </c>
-      <c r="C7" s="117">
-        <v>46294</v>
-      </c>
-      <c r="D7" s="117">
-        <v>46308</v>
-      </c>
-      <c r="E7" s="122">
-        <v>43</v>
-      </c>
-      <c r="F7" s="119" t="s">
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="121"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="120"/>
+    </row>
+    <row r="8" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="51">
+        <v>4</v>
+      </c>
+      <c r="B8" s="123" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="124">
+        <v>46315</v>
+      </c>
+      <c r="D8" s="124">
+        <v>46329</v>
+      </c>
+      <c r="E8" s="125">
+        <v>46</v>
+      </c>
+      <c r="F8" s="126" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="123"/>
-      <c r="K7" s="121"/>
-    </row>
-    <row r="8" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="52">
-        <v>4</v>
-      </c>
-      <c r="B8" s="124" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="125">
-        <v>46315</v>
-      </c>
-      <c r="D8" s="125">
-        <v>46329</v>
-      </c>
-      <c r="E8" s="126">
-        <v>46</v>
-      </c>
-      <c r="F8" s="127" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="126"/>
-      <c r="J8" s="128"/>
-      <c r="K8" s="129"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="127"/>
+      <c r="K8" s="128"/>
     </row>
     <row r="9" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="52">
+      <c r="A9" s="51">
         <v>5</v>
       </c>
-      <c r="B9" s="124"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="127"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="128"/>
-      <c r="K9" s="129"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="127"/>
+      <c r="K9" s="128"/>
     </row>
     <row r="10" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="52">
+      <c r="A10" s="51">
         <v>6</v>
       </c>
-      <c r="B10" s="124"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="126"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="125"/>
-      <c r="I10" s="126"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="129"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="127"/>
+      <c r="K10" s="128"/>
     </row>
     <row r="11" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="52">
+      <c r="A11" s="51">
         <v>7</v>
       </c>
-      <c r="B11" s="124"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="126"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="128"/>
-      <c r="K11" s="129"/>
+      <c r="B11" s="123"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="128"/>
     </row>
     <row r="12" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="52">
+      <c r="A12" s="51">
         <v>8</v>
       </c>
-      <c r="B12" s="124"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="129"/>
+      <c r="B12" s="123"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="128"/>
     </row>
     <row r="13" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="52">
+      <c r="A13" s="51">
         <v>9</v>
       </c>
-      <c r="B13" s="124"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="125"/>
-      <c r="H13" s="125"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="129"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="124"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="128"/>
     </row>
     <row r="14" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="52">
+      <c r="A14" s="51">
         <v>10</v>
       </c>
-      <c r="B14" s="124"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="126"/>
-      <c r="J14" s="128"/>
-      <c r="K14" s="129"/>
+      <c r="B14" s="123"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="124"/>
+      <c r="H14" s="124"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="128"/>
     </row>
     <row r="15" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="53"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="56">
+      <c r="A15" s="52"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="55">
         <f>SUM(E5:E14)</f>
         <v>130</v>
       </c>
-      <c r="F15" s="54"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="56">
+      <c r="F15" s="53"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="55">
         <f>SUM(I5:I14)</f>
-        <v>10.5</v>
-      </c>
-      <c r="J15" s="58">
+        <v>66.5</v>
+      </c>
+      <c r="J15" s="57">
         <f>SUM(J5:J14)</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="57"/>
+        <v>25</v>
+      </c>
+      <c r="K15" s="56"/>
     </row>
     <row r="16" spans="1:11" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="J16" s="21"/>
+      <c r="J16" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10388,631 +10356,637 @@
   <dimension ref="A1:AMJ60"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.59765625" style="61" customWidth="1"/>
-    <col min="2" max="2" width="35.59765625" style="61" customWidth="1"/>
-    <col min="3" max="3" width="6.5" style="61" customWidth="1"/>
-    <col min="4" max="4" width="13.19921875" style="61" customWidth="1"/>
-    <col min="5" max="5" width="8.8984375" style="61" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="61" customWidth="1"/>
-    <col min="7" max="7" width="9.09765625" style="61" customWidth="1"/>
-    <col min="8" max="9" width="12.19921875" style="61" customWidth="1"/>
-    <col min="10" max="10" width="24.19921875" style="61" customWidth="1"/>
-    <col min="11" max="11" width="27.8984375" style="61" customWidth="1"/>
-    <col min="12" max="12" width="8.5" style="61" customWidth="1"/>
-    <col min="13" max="14" width="20.5" style="61" customWidth="1"/>
-    <col min="15" max="256" width="8.5" style="61" customWidth="1"/>
-    <col min="257" max="258" width="6.5" style="61" customWidth="1"/>
-    <col min="259" max="259" width="13.8984375" style="61" customWidth="1"/>
-    <col min="260" max="260" width="9" style="61" customWidth="1"/>
-    <col min="261" max="261" width="13.5" style="61" customWidth="1"/>
-    <col min="262" max="262" width="10" style="61" customWidth="1"/>
-    <col min="263" max="263" width="12.19921875" style="61" customWidth="1"/>
-    <col min="264" max="264" width="5.8984375" style="61" customWidth="1"/>
-    <col min="265" max="265" width="24.19921875" style="61" customWidth="1"/>
-    <col min="266" max="266" width="32.5" style="61" customWidth="1"/>
-    <col min="267" max="267" width="17.59765625" style="61" customWidth="1"/>
-    <col min="268" max="268" width="8.5" style="61" customWidth="1"/>
-    <col min="269" max="270" width="20.5" style="61" customWidth="1"/>
-    <col min="271" max="512" width="8.5" style="61" customWidth="1"/>
-    <col min="513" max="514" width="6.5" style="61" customWidth="1"/>
-    <col min="515" max="515" width="13.8984375" style="61" customWidth="1"/>
-    <col min="516" max="516" width="9" style="61" customWidth="1"/>
-    <col min="517" max="517" width="13.5" style="61" customWidth="1"/>
-    <col min="518" max="518" width="10" style="61" customWidth="1"/>
-    <col min="519" max="519" width="12.19921875" style="61" customWidth="1"/>
-    <col min="520" max="520" width="5.8984375" style="61" customWidth="1"/>
-    <col min="521" max="521" width="24.19921875" style="61" customWidth="1"/>
-    <col min="522" max="522" width="32.5" style="61" customWidth="1"/>
-    <col min="523" max="523" width="17.59765625" style="61" customWidth="1"/>
-    <col min="524" max="524" width="8.5" style="61" customWidth="1"/>
-    <col min="525" max="526" width="20.5" style="61" customWidth="1"/>
-    <col min="527" max="768" width="8.5" style="61" customWidth="1"/>
-    <col min="769" max="770" width="6.5" style="61" customWidth="1"/>
-    <col min="771" max="771" width="13.8984375" style="61" customWidth="1"/>
-    <col min="772" max="772" width="9" style="61" customWidth="1"/>
-    <col min="773" max="773" width="13.5" style="61" customWidth="1"/>
-    <col min="774" max="774" width="10" style="61" customWidth="1"/>
-    <col min="775" max="775" width="12.19921875" style="61" customWidth="1"/>
-    <col min="776" max="776" width="5.8984375" style="61" customWidth="1"/>
-    <col min="777" max="777" width="24.19921875" style="61" customWidth="1"/>
-    <col min="778" max="778" width="32.5" style="61" customWidth="1"/>
-    <col min="779" max="779" width="17.59765625" style="61" customWidth="1"/>
-    <col min="780" max="780" width="8.5" style="61" customWidth="1"/>
-    <col min="781" max="782" width="20.5" style="61" customWidth="1"/>
-    <col min="783" max="1024" width="8.5" style="61" customWidth="1"/>
+    <col min="1" max="1" width="5.59765625" style="60" customWidth="1"/>
+    <col min="2" max="2" width="35.59765625" style="60" customWidth="1"/>
+    <col min="3" max="3" width="6.5" style="60" customWidth="1"/>
+    <col min="4" max="4" width="13.19921875" style="60" customWidth="1"/>
+    <col min="5" max="5" width="8.8984375" style="60" customWidth="1"/>
+    <col min="6" max="6" width="12.5" style="60" customWidth="1"/>
+    <col min="7" max="7" width="9.09765625" style="60" customWidth="1"/>
+    <col min="8" max="9" width="12.19921875" style="60" customWidth="1"/>
+    <col min="10" max="10" width="24.19921875" style="60" customWidth="1"/>
+    <col min="11" max="11" width="27.8984375" style="60" customWidth="1"/>
+    <col min="12" max="12" width="8.5" style="60" customWidth="1"/>
+    <col min="13" max="14" width="20.5" style="60" customWidth="1"/>
+    <col min="15" max="256" width="8.5" style="60" customWidth="1"/>
+    <col min="257" max="258" width="6.5" style="60" customWidth="1"/>
+    <col min="259" max="259" width="13.8984375" style="60" customWidth="1"/>
+    <col min="260" max="260" width="9" style="60" customWidth="1"/>
+    <col min="261" max="261" width="13.5" style="60" customWidth="1"/>
+    <col min="262" max="262" width="10" style="60" customWidth="1"/>
+    <col min="263" max="263" width="12.19921875" style="60" customWidth="1"/>
+    <col min="264" max="264" width="5.8984375" style="60" customWidth="1"/>
+    <col min="265" max="265" width="24.19921875" style="60" customWidth="1"/>
+    <col min="266" max="266" width="32.5" style="60" customWidth="1"/>
+    <col min="267" max="267" width="17.59765625" style="60" customWidth="1"/>
+    <col min="268" max="268" width="8.5" style="60" customWidth="1"/>
+    <col min="269" max="270" width="20.5" style="60" customWidth="1"/>
+    <col min="271" max="512" width="8.5" style="60" customWidth="1"/>
+    <col min="513" max="514" width="6.5" style="60" customWidth="1"/>
+    <col min="515" max="515" width="13.8984375" style="60" customWidth="1"/>
+    <col min="516" max="516" width="9" style="60" customWidth="1"/>
+    <col min="517" max="517" width="13.5" style="60" customWidth="1"/>
+    <col min="518" max="518" width="10" style="60" customWidth="1"/>
+    <col min="519" max="519" width="12.19921875" style="60" customWidth="1"/>
+    <col min="520" max="520" width="5.8984375" style="60" customWidth="1"/>
+    <col min="521" max="521" width="24.19921875" style="60" customWidth="1"/>
+    <col min="522" max="522" width="32.5" style="60" customWidth="1"/>
+    <col min="523" max="523" width="17.59765625" style="60" customWidth="1"/>
+    <col min="524" max="524" width="8.5" style="60" customWidth="1"/>
+    <col min="525" max="526" width="20.5" style="60" customWidth="1"/>
+    <col min="527" max="768" width="8.5" style="60" customWidth="1"/>
+    <col min="769" max="770" width="6.5" style="60" customWidth="1"/>
+    <col min="771" max="771" width="13.8984375" style="60" customWidth="1"/>
+    <col min="772" max="772" width="9" style="60" customWidth="1"/>
+    <col min="773" max="773" width="13.5" style="60" customWidth="1"/>
+    <col min="774" max="774" width="10" style="60" customWidth="1"/>
+    <col min="775" max="775" width="12.19921875" style="60" customWidth="1"/>
+    <col min="776" max="776" width="5.8984375" style="60" customWidth="1"/>
+    <col min="777" max="777" width="24.19921875" style="60" customWidth="1"/>
+    <col min="778" max="778" width="32.5" style="60" customWidth="1"/>
+    <col min="779" max="779" width="17.59765625" style="60" customWidth="1"/>
+    <col min="780" max="780" width="8.5" style="60" customWidth="1"/>
+    <col min="781" max="782" width="20.5" style="60" customWidth="1"/>
+    <col min="783" max="1024" width="8.5" style="60" customWidth="1"/>
     <col min="1025" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="60" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="130" t="s">
+    <row r="1" spans="1:11" s="59" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="139" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
     </row>
     <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="62" t="s">
+      <c r="D3" s="61" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="62" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="62" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="63" t="s">
+      <c r="D7" s="62" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="62" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D10" s="63" t="s">
+      <c r="D10" s="62" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="63" t="s">
+      <c r="D11" s="62" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="62" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="63" t="s">
+      <c r="D13" s="62" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="62" t="s">
+      <c r="D14" s="61" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="63" t="s">
+      <c r="D15" s="62" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="62" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="17" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="63" t="s">
+      <c r="D17" s="62" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="18" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="62" t="s">
+      <c r="D18" s="61" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="19" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="63" t="s">
+      <c r="D19" s="62" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="20" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="63" t="s">
+      <c r="D20" s="62" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="21" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="63" t="s">
+      <c r="D21" s="62" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="22" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="62" t="s">
+      <c r="D22" s="61" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="23" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="63" t="s">
+      <c r="D23" s="62" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="24" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="63" t="s">
+      <c r="D24" s="62" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="25" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="63" t="s">
+      <c r="D25" s="62" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="26" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="63" t="s">
+      <c r="D26" s="62" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="27" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D27" s="62" t="s">
+      <c r="D27" s="61" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="28" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="63" t="s">
+      <c r="D28" s="62" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="29" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="63" t="s">
+      <c r="D29" s="62" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="30" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="63" t="s">
+      <c r="D30" s="62" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="4:4" s="64" customFormat="1" ht="10.199999999999999" hidden="1" x14ac:dyDescent="0.2">
-      <c r="D31" s="65" t="s">
+    <row r="31" spans="4:4" s="63" customFormat="1" ht="10.199999999999999" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D31" s="64" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="32" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="66" t="s">
+      <c r="D32" s="65" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="145" t="s">
+      <c r="D33" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="E33" s="145"/>
+      <c r="E33" s="150"/>
     </row>
     <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D34" s="63">
+      <c r="D34" s="62">
         <v>4290</v>
       </c>
-      <c r="E34" s="63" t="s">
+      <c r="E34" s="62" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D35" s="63">
+      <c r="D35" s="62">
         <v>5082</v>
       </c>
-      <c r="E35" s="63" t="s">
+      <c r="E35" s="62" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D36" s="63">
+      <c r="D36" s="62">
         <v>4356</v>
       </c>
-      <c r="E36" s="63" t="s">
+      <c r="E36" s="62" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="63">
+      <c r="D37" s="62">
         <v>5929</v>
       </c>
-      <c r="E37" s="63" t="s">
+      <c r="E37" s="62" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="63">
+      <c r="D38" s="62">
         <v>5005</v>
       </c>
-      <c r="E38" s="63" t="s">
+      <c r="E38" s="62" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="63">
+      <c r="D39" s="62">
         <v>4225</v>
       </c>
-      <c r="E39" s="63" t="s">
+      <c r="E39" s="62" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:11" s="60" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="146" t="s">
+    <row r="41" spans="1:11" s="59" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="B41" s="146"/>
-      <c r="C41" s="146"/>
-      <c r="D41" s="146"/>
-      <c r="E41" s="146"/>
-      <c r="F41" s="146"/>
-      <c r="G41" s="146"/>
-      <c r="H41" s="146"/>
-      <c r="I41" s="146"/>
-      <c r="J41" s="146"/>
-      <c r="K41" s="146"/>
-    </row>
-    <row r="42" spans="1:11" s="60" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="147" t="s">
+      <c r="B41" s="151"/>
+      <c r="C41" s="151"/>
+      <c r="D41" s="151"/>
+      <c r="E41" s="151"/>
+      <c r="F41" s="151"/>
+      <c r="G41" s="151"/>
+      <c r="H41" s="151"/>
+      <c r="I41" s="151"/>
+      <c r="J41" s="151"/>
+      <c r="K41" s="151"/>
+    </row>
+    <row r="42" spans="1:11" s="59" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="147"/>
-      <c r="C42" s="147"/>
-      <c r="D42" s="147"/>
-      <c r="E42" s="147"/>
-      <c r="F42" s="147"/>
-      <c r="G42" s="147"/>
-      <c r="H42" s="147"/>
-      <c r="I42" s="147"/>
-      <c r="J42" s="147"/>
-      <c r="K42" s="147"/>
-    </row>
-    <row r="43" spans="1:11" s="60" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="148" t="s">
+      <c r="B42" s="152"/>
+      <c r="C42" s="152"/>
+      <c r="D42" s="152"/>
+      <c r="E42" s="152"/>
+      <c r="F42" s="152"/>
+      <c r="G42" s="152"/>
+      <c r="H42" s="152"/>
+      <c r="I42" s="152"/>
+      <c r="J42" s="152"/>
+      <c r="K42" s="152"/>
+    </row>
+    <row r="43" spans="1:11" s="59" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="153" t="s">
         <v>122</v>
       </c>
-      <c r="B43" s="148"/>
-      <c r="C43" s="148"/>
-      <c r="D43" s="148"/>
-      <c r="E43" s="148"/>
-      <c r="F43" s="148"/>
-      <c r="G43" s="148"/>
-      <c r="H43" s="148"/>
-      <c r="I43" s="148"/>
-      <c r="J43" s="148"/>
-      <c r="K43" s="148"/>
-    </row>
-    <row r="44" spans="1:11" s="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="144" t="s">
+      <c r="B43" s="153"/>
+      <c r="C43" s="153"/>
+      <c r="D43" s="153"/>
+      <c r="E43" s="153"/>
+      <c r="F43" s="153"/>
+      <c r="G43" s="153"/>
+      <c r="H43" s="153"/>
+      <c r="I43" s="153"/>
+      <c r="J43" s="153"/>
+      <c r="K43" s="153"/>
+    </row>
+    <row r="44" spans="1:11" s="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="149" t="s">
         <v>123</v>
       </c>
-      <c r="B44" s="144"/>
-      <c r="C44" s="144"/>
-      <c r="D44" s="144"/>
-      <c r="E44" s="144"/>
-      <c r="F44" s="144"/>
-      <c r="G44" s="144"/>
-      <c r="H44" s="144"/>
-      <c r="I44" s="144"/>
-      <c r="J44" s="144"/>
-      <c r="K44" s="144"/>
+      <c r="B44" s="149"/>
+      <c r="C44" s="149"/>
+      <c r="D44" s="149"/>
+      <c r="E44" s="149"/>
+      <c r="F44" s="149"/>
+      <c r="G44" s="149"/>
+      <c r="H44" s="149"/>
+      <c r="I44" s="149"/>
+      <c r="J44" s="149"/>
+      <c r="K44" s="149"/>
     </row>
     <row r="45" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="151" t="s">
+      <c r="A46" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="B46" s="151"/>
-      <c r="C46" s="151"/>
-      <c r="D46" s="151"/>
-      <c r="E46" s="151"/>
-      <c r="F46" s="151"/>
-      <c r="G46" s="151"/>
-      <c r="H46" s="151"/>
-      <c r="I46" s="151"/>
-      <c r="J46" s="151"/>
-      <c r="K46" s="151"/>
-    </row>
-    <row r="47" spans="1:11" s="69" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="67" t="s">
+      <c r="B46" s="145"/>
+      <c r="C46" s="145"/>
+      <c r="D46" s="145"/>
+      <c r="E46" s="145"/>
+      <c r="F46" s="145"/>
+      <c r="G46" s="145"/>
+      <c r="H46" s="145"/>
+      <c r="I46" s="145"/>
+      <c r="J46" s="145"/>
+      <c r="K46" s="145"/>
+    </row>
+    <row r="47" spans="1:11" s="68" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="B47" s="68"/>
-      <c r="C47" s="152" t="s">
+      <c r="B47" s="67"/>
+      <c r="C47" s="146" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="152"/>
-      <c r="E47" s="152"/>
-      <c r="F47" s="152"/>
-      <c r="G47" s="152"/>
-      <c r="H47" s="152"/>
-      <c r="I47" s="152"/>
-      <c r="J47" s="152"/>
-      <c r="K47" s="152"/>
-    </row>
-    <row r="48" spans="1:11" s="71" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="153"/>
-      <c r="B48" s="149" t="s">
+      <c r="D47" s="146"/>
+      <c r="E47" s="146"/>
+      <c r="F47" s="146"/>
+      <c r="G47" s="146"/>
+      <c r="H47" s="146"/>
+      <c r="I47" s="146"/>
+      <c r="J47" s="146"/>
+      <c r="K47" s="146"/>
+    </row>
+    <row r="48" spans="1:11" s="70" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="147"/>
+      <c r="B48" s="143" t="s">
         <v>127</v>
       </c>
-      <c r="C48" s="149" t="s">
+      <c r="C48" s="143" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="149" t="s">
+      <c r="D48" s="143" t="s">
         <v>129</v>
       </c>
-      <c r="E48" s="149" t="s">
+      <c r="E48" s="143" t="s">
         <v>98</v>
       </c>
-      <c r="F48" s="149" t="s">
+      <c r="F48" s="143" t="s">
         <v>130</v>
       </c>
-      <c r="G48" s="149" t="s">
+      <c r="G48" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="H48" s="154" t="s">
+      <c r="H48" s="148" t="s">
         <v>131</v>
       </c>
-      <c r="I48" s="154"/>
-      <c r="J48" s="154"/>
-      <c r="K48" s="154"/>
-    </row>
-    <row r="49" spans="1:11" s="71" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="153"/>
-      <c r="B49" s="149"/>
-      <c r="C49" s="149"/>
-      <c r="D49" s="149"/>
-      <c r="E49" s="149"/>
-      <c r="F49" s="149"/>
-      <c r="G49" s="149"/>
-      <c r="H49" s="149" t="s">
+      <c r="I48" s="148"/>
+      <c r="J48" s="148"/>
+      <c r="K48" s="148"/>
+    </row>
+    <row r="49" spans="1:11" s="70" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="147"/>
+      <c r="B49" s="143"/>
+      <c r="C49" s="143"/>
+      <c r="D49" s="143"/>
+      <c r="E49" s="143"/>
+      <c r="F49" s="143"/>
+      <c r="G49" s="143"/>
+      <c r="H49" s="143" t="s">
         <v>132</v>
       </c>
-      <c r="I49" s="149"/>
-      <c r="J49" s="70" t="s">
+      <c r="I49" s="143"/>
+      <c r="J49" s="69" t="s">
         <v>133</v>
       </c>
-      <c r="K49" s="70" t="s">
+      <c r="K49" s="69" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="71" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.25">
-      <c r="A50" s="72">
+    <row r="50" spans="1:11" s="70" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A50" s="71">
         <v>1</v>
       </c>
-      <c r="B50" s="73" t="s">
+      <c r="B50" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="C50" s="74">
+      <c r="C50" s="73">
         <v>46252</v>
       </c>
-      <c r="D50" s="75" t="s">
+      <c r="D50" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="E50" s="75" t="s">
+      <c r="E50" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="F50" s="76" t="str">
+      <c r="F50" s="75" t="str">
         <f t="shared" ref="F50:F60" si="0">IF(OR((CODE($D50)*CODE($E50))=$D$36,(CODE($D50)*CODE($E50))=$D$35),$D$15,IF(OR((CODE($D50)*CODE($E50))=$D$34,(CODE($D50)*CODE($E50))=$D$37),$D$16,IF(OR((CODE($D50)*CODE($E50))=$D$38,(CODE($D50)*CODE($E50))=$D$39),$D$17,0)))</f>
         <v>Alta</v>
       </c>
-      <c r="G50" s="75" t="s">
+      <c r="G50" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="H50" s="150"/>
-      <c r="I50" s="150"/>
-      <c r="J50" s="77" t="s">
+      <c r="H50" s="144"/>
+      <c r="I50" s="144"/>
+      <c r="J50" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="K50" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="K50" s="77" t="s">
+    </row>
+    <row r="51" spans="1:11" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+      <c r="A51" s="71">
+        <v>2</v>
+      </c>
+      <c r="B51" s="72" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" s="71" customFormat="1" ht="51" x14ac:dyDescent="0.25">
-      <c r="A51" s="72">
-        <v>2</v>
-      </c>
-      <c r="B51" s="73" t="s">
-        <v>228</v>
-      </c>
-      <c r="C51" s="74">
+      <c r="C51" s="73">
         <v>46252</v>
       </c>
-      <c r="D51" s="75" t="s">
+      <c r="D51" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="E51" s="75" t="s">
+      <c r="E51" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="F51" s="76" t="str">
+      <c r="F51" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Alta</v>
       </c>
-      <c r="G51" s="75" t="s">
+      <c r="G51" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="H51" s="78"/>
-      <c r="I51" s="79"/>
-      <c r="J51" s="77" t="s">
+      <c r="H51" s="77"/>
+      <c r="I51" s="78"/>
+      <c r="J51" s="76" t="s">
+        <v>228</v>
+      </c>
+      <c r="K51" s="76" t="s">
         <v>229</v>
       </c>
-      <c r="K51" s="77" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" s="71" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="72"/>
-      <c r="B52" s="73"/>
-      <c r="C52" s="74"/>
-      <c r="D52" s="75"/>
-      <c r="E52" s="75"/>
-      <c r="F52" s="76" t="e">
+    </row>
+    <row r="52" spans="1:11" s="70" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="71"/>
+      <c r="B52" s="72"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="74"/>
+      <c r="E52" s="74"/>
+      <c r="F52" s="75" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G52" s="75"/>
-      <c r="H52" s="78"/>
-      <c r="I52" s="79"/>
-      <c r="J52" s="77"/>
-      <c r="K52" s="77"/>
-    </row>
-    <row r="53" spans="1:11" s="71" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="72"/>
-      <c r="B53" s="73"/>
-      <c r="C53" s="74"/>
-      <c r="D53" s="75"/>
-      <c r="E53" s="75"/>
-      <c r="F53" s="76" t="e">
+      <c r="G52" s="74"/>
+      <c r="H52" s="77"/>
+      <c r="I52" s="78"/>
+      <c r="J52" s="76"/>
+      <c r="K52" s="76"/>
+    </row>
+    <row r="53" spans="1:11" s="70" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="71"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="73"/>
+      <c r="D53" s="74"/>
+      <c r="E53" s="74"/>
+      <c r="F53" s="75" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G53" s="75"/>
-      <c r="H53" s="78"/>
-      <c r="I53" s="79"/>
-      <c r="J53" s="77"/>
-      <c r="K53" s="77"/>
-    </row>
-    <row r="54" spans="1:11" s="71" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="72"/>
-      <c r="B54" s="73"/>
-      <c r="C54" s="74"/>
-      <c r="D54" s="75"/>
-      <c r="E54" s="75"/>
-      <c r="F54" s="76" t="e">
+      <c r="G53" s="74"/>
+      <c r="H53" s="77"/>
+      <c r="I53" s="78"/>
+      <c r="J53" s="76"/>
+      <c r="K53" s="76"/>
+    </row>
+    <row r="54" spans="1:11" s="70" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="71"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="73"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="75" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G54" s="75"/>
-      <c r="H54" s="78"/>
-      <c r="I54" s="79"/>
-      <c r="J54" s="77"/>
-      <c r="K54" s="77"/>
-    </row>
-    <row r="55" spans="1:11" s="71" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="72"/>
-      <c r="B55" s="73"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="75"/>
-      <c r="E55" s="75"/>
-      <c r="F55" s="76" t="e">
+      <c r="G54" s="74"/>
+      <c r="H54" s="77"/>
+      <c r="I54" s="78"/>
+      <c r="J54" s="76"/>
+      <c r="K54" s="76"/>
+    </row>
+    <row r="55" spans="1:11" s="70" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="71"/>
+      <c r="B55" s="72"/>
+      <c r="C55" s="73"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="74"/>
+      <c r="F55" s="75" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G55" s="75"/>
-      <c r="H55" s="78"/>
-      <c r="I55" s="79"/>
-      <c r="J55" s="77"/>
-      <c r="K55" s="77"/>
-    </row>
-    <row r="56" spans="1:11" s="71" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="72"/>
-      <c r="B56" s="73"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="75"/>
-      <c r="E56" s="75"/>
-      <c r="F56" s="76" t="e">
+      <c r="G55" s="74"/>
+      <c r="H55" s="77"/>
+      <c r="I55" s="78"/>
+      <c r="J55" s="76"/>
+      <c r="K55" s="76"/>
+    </row>
+    <row r="56" spans="1:11" s="70" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="71"/>
+      <c r="B56" s="72"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="74"/>
+      <c r="E56" s="74"/>
+      <c r="F56" s="75" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G56" s="75"/>
-      <c r="H56" s="78"/>
-      <c r="I56" s="79"/>
-      <c r="J56" s="77"/>
-      <c r="K56" s="77"/>
-    </row>
-    <row r="57" spans="1:11" s="71" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="72"/>
-      <c r="B57" s="73"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="75"/>
-      <c r="E57" s="75"/>
-      <c r="F57" s="76" t="e">
+      <c r="G56" s="74"/>
+      <c r="H56" s="77"/>
+      <c r="I56" s="78"/>
+      <c r="J56" s="76"/>
+      <c r="K56" s="76"/>
+    </row>
+    <row r="57" spans="1:11" s="70" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="71"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="74"/>
+      <c r="E57" s="74"/>
+      <c r="F57" s="75" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G57" s="75"/>
-      <c r="H57" s="78"/>
-      <c r="I57" s="79"/>
-      <c r="J57" s="77"/>
-      <c r="K57" s="77"/>
-    </row>
-    <row r="58" spans="1:11" s="71" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
-      <c r="B58" s="73"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="75"/>
-      <c r="E58" s="75"/>
-      <c r="F58" s="76" t="e">
+      <c r="G57" s="74"/>
+      <c r="H57" s="77"/>
+      <c r="I57" s="78"/>
+      <c r="J57" s="76"/>
+      <c r="K57" s="76"/>
+    </row>
+    <row r="58" spans="1:11" s="70" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="71"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="74"/>
+      <c r="E58" s="74"/>
+      <c r="F58" s="75" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G58" s="75"/>
-      <c r="H58" s="78"/>
-      <c r="I58" s="79"/>
-      <c r="J58" s="77"/>
-      <c r="K58" s="77"/>
-    </row>
-    <row r="59" spans="1:11" s="71" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="72"/>
-      <c r="B59" s="73"/>
-      <c r="C59" s="74"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="75"/>
-      <c r="F59" s="76" t="e">
+      <c r="G58" s="74"/>
+      <c r="H58" s="77"/>
+      <c r="I58" s="78"/>
+      <c r="J58" s="76"/>
+      <c r="K58" s="76"/>
+    </row>
+    <row r="59" spans="1:11" s="70" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="71"/>
+      <c r="B59" s="72"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="74"/>
+      <c r="E59" s="74"/>
+      <c r="F59" s="75" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G59" s="75"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="77"/>
-      <c r="K59" s="77"/>
-    </row>
-    <row r="60" spans="1:11" s="71" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
-      <c r="B60" s="73"/>
-      <c r="C60" s="74"/>
-      <c r="D60" s="75"/>
-      <c r="E60" s="75"/>
-      <c r="F60" s="76" t="e">
+      <c r="G59" s="74"/>
+      <c r="H59" s="144"/>
+      <c r="I59" s="144"/>
+      <c r="J59" s="76"/>
+      <c r="K59" s="76"/>
+    </row>
+    <row r="60" spans="1:11" s="70" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="71"/>
+      <c r="B60" s="72"/>
+      <c r="C60" s="73"/>
+      <c r="D60" s="74"/>
+      <c r="E60" s="74"/>
+      <c r="F60" s="75" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G60" s="75"/>
-      <c r="H60" s="150"/>
-      <c r="I60" s="150"/>
-      <c r="J60" s="77"/>
-      <c r="K60" s="77"/>
+      <c r="G60" s="74"/>
+      <c r="H60" s="144"/>
+      <c r="I60" s="144"/>
+      <c r="J60" s="76"/>
+      <c r="K60" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="H49:I49"/>
     <mergeCell ref="H50:I50"/>
     <mergeCell ref="H59:I59"/>
@@ -11027,12 +11001,6 @@
     <mergeCell ref="F48:F49"/>
     <mergeCell ref="G48:G49"/>
     <mergeCell ref="H48:K48"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A43:K43"/>
   </mergeCells>
   <conditionalFormatting sqref="F50:F60">
     <cfRule type="cellIs" dxfId="2" priority="8" stopIfTrue="1" operator="equal">
@@ -11089,432 +11057,432 @@
     <col min="1025" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="60" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="157" t="s">
+    <row r="1" spans="1:23" s="59" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="156" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157"/>
-      <c r="M1" s="157"/>
-      <c r="N1" s="157"/>
-    </row>
-    <row r="2" spans="1:23" s="80" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="158" t="s">
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+    </row>
+    <row r="2" spans="1:23" s="79" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="157" t="s">
         <v>120</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-    </row>
-    <row r="3" spans="1:23" s="80" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="159" t="s">
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+    </row>
+    <row r="3" spans="1:23" s="79" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="158" t="s">
         <v>137</v>
       </c>
-      <c r="B3" s="159"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="159"/>
-      <c r="J3" s="159"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="159"/>
-    </row>
-    <row r="4" spans="1:23" s="80" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="160" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="158"/>
+    </row>
+    <row r="4" spans="1:23" s="79" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="159" t="s">
         <v>138</v>
       </c>
-      <c r="B4" s="160"/>
-      <c r="C4" s="160"/>
-      <c r="D4" s="160"/>
-      <c r="E4" s="160"/>
-      <c r="F4" s="160"/>
-      <c r="G4" s="160"/>
-      <c r="H4" s="160"/>
-      <c r="I4" s="160"/>
-      <c r="J4" s="160"/>
-      <c r="K4" s="160"/>
-      <c r="L4" s="160"/>
-      <c r="M4" s="160"/>
-      <c r="N4" s="160"/>
-    </row>
-    <row r="5" spans="1:23" s="80" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="161" t="s">
+      <c r="B4" s="159"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
+      <c r="H4" s="159"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="159"/>
+      <c r="K4" s="159"/>
+      <c r="L4" s="159"/>
+      <c r="M4" s="159"/>
+      <c r="N4" s="159"/>
+    </row>
+    <row r="5" spans="1:23" s="79" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="160" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="161"/>
-      <c r="C5" s="161"/>
-      <c r="D5" s="161"/>
-      <c r="E5" s="161"/>
-      <c r="F5" s="161"/>
-      <c r="G5" s="161"/>
-      <c r="H5" s="161"/>
-      <c r="I5" s="161"/>
-      <c r="J5" s="161"/>
-      <c r="K5" s="161"/>
-      <c r="L5" s="161"/>
-      <c r="M5" s="161"/>
-      <c r="N5" s="161"/>
+      <c r="B5" s="160"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="160"/>
+      <c r="L5" s="160"/>
+      <c r="M5" s="160"/>
+      <c r="N5" s="160"/>
     </row>
     <row r="6" spans="1:23" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:23" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="155" t="s">
+      <c r="A7" s="154" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="155"/>
-      <c r="D7" s="155" t="s">
+      <c r="B7" s="154"/>
+      <c r="D7" s="154" t="s">
         <v>141</v>
       </c>
-      <c r="E7" s="155"/>
-      <c r="G7" s="155" t="s">
+      <c r="E7" s="154"/>
+      <c r="G7" s="154" t="s">
         <v>142</v>
       </c>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="155"/>
-      <c r="K7" s="155"/>
-      <c r="M7" s="155" t="s">
+      <c r="H7" s="154"/>
+      <c r="I7" s="154"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="154"/>
+      <c r="M7" s="154" t="s">
         <v>143</v>
       </c>
-      <c r="N7" s="155"/>
+      <c r="N7" s="154"/>
     </row>
     <row r="8" spans="1:23" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="82" t="s">
         <v>144</v>
       </c>
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="83" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="83" t="s">
+      <c r="D8" s="82" t="s">
         <v>146</v>
       </c>
-      <c r="E8" s="84" t="s">
+      <c r="E8" s="83" t="s">
         <v>145</v>
       </c>
-      <c r="G8" s="83" t="s">
+      <c r="G8" s="82" t="s">
         <v>147</v>
       </c>
-      <c r="H8" s="83" t="s">
+      <c r="H8" s="82" t="s">
         <v>148</v>
       </c>
-      <c r="I8" s="83" t="s">
+      <c r="I8" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="J8" s="84" t="s">
+      <c r="J8" s="83" t="s">
         <v>149</v>
       </c>
-      <c r="K8" s="84" t="s">
+      <c r="K8" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="M8" s="84" t="s">
+      <c r="M8" s="83" t="s">
         <v>151</v>
       </c>
-      <c r="N8" s="84" t="s">
+      <c r="N8" s="83" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="80" t="s">
         <v>153</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="81" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="81" t="s">
+      <c r="D9" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="E9" s="82" t="s">
+      <c r="E9" s="81" t="s">
         <v>148</v>
       </c>
-      <c r="G9" s="83" t="s">
+      <c r="G9" s="82" t="s">
         <v>155</v>
       </c>
-      <c r="H9" s="81">
+      <c r="H9" s="80">
         <v>2</v>
       </c>
-      <c r="I9" s="81">
+      <c r="I9" s="80">
         <v>0</v>
       </c>
-      <c r="J9" s="81">
+      <c r="J9" s="80">
         <v>0</v>
       </c>
-      <c r="K9" s="84">
+      <c r="K9" s="83">
         <f>(H9*4)+(I9*6)+(J9*8)</f>
         <v>8</v>
       </c>
-      <c r="M9" s="85" t="s">
+      <c r="M9" s="84" t="s">
         <v>156</v>
       </c>
-      <c r="N9" s="86"/>
+      <c r="N9" s="85"/>
     </row>
     <row r="10" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="82" t="s">
+      <c r="B10" s="81" t="s">
         <v>148</v>
       </c>
-      <c r="D10" s="81"/>
-      <c r="E10" s="82"/>
-      <c r="G10" s="83" t="s">
+      <c r="D10" s="80"/>
+      <c r="E10" s="81"/>
+      <c r="G10" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="84">
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="83">
         <f>(H10*3)+(I10*4)+(J10*6)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="85" t="s">
+      <c r="M10" s="84" t="s">
         <v>159</v>
       </c>
-      <c r="N10" s="86"/>
+      <c r="N10" s="85"/>
     </row>
     <row r="11" spans="1:23" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="81"/>
-      <c r="B11" s="82"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="82"/>
-      <c r="G11" s="155" t="s">
+      <c r="A11" s="80"/>
+      <c r="B11" s="81"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="81"/>
+      <c r="G11" s="154" t="s">
         <v>160</v>
       </c>
-      <c r="H11" s="155"/>
-      <c r="I11" s="155"/>
-      <c r="J11" s="155"/>
-      <c r="K11" s="155"/>
-      <c r="M11" s="85" t="s">
+      <c r="H11" s="154"/>
+      <c r="I11" s="154"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="154"/>
+      <c r="M11" s="84" t="s">
         <v>161</v>
       </c>
-      <c r="N11" s="86"/>
+      <c r="N11" s="85"/>
     </row>
     <row r="12" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A12" s="81"/>
-      <c r="B12" s="82"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="82"/>
-      <c r="G12" s="83" t="s">
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="81"/>
+      <c r="G12" s="82" t="s">
         <v>147</v>
       </c>
-      <c r="H12" s="83" t="s">
+      <c r="H12" s="82" t="s">
         <v>148</v>
       </c>
-      <c r="I12" s="83" t="s">
+      <c r="I12" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="84" t="s">
+      <c r="J12" s="83" t="s">
         <v>149</v>
       </c>
-      <c r="K12" s="84" t="s">
+      <c r="K12" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="M12" s="85" t="s">
+      <c r="M12" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="N12" s="86"/>
+      <c r="N12" s="85"/>
     </row>
     <row r="13" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A13" s="81"/>
-      <c r="B13" s="82"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="82"/>
-      <c r="G13" s="83" t="s">
+      <c r="A13" s="80"/>
+      <c r="B13" s="81"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="81"/>
+      <c r="G13" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="H13" s="81">
+      <c r="H13" s="80">
         <v>1</v>
       </c>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="84">
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="83">
         <f>(H13*3)+(I13*4)+(J13*6)</f>
         <v>3</v>
       </c>
-      <c r="M13" s="85" t="s">
+      <c r="M13" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="N13" s="86"/>
+      <c r="N13" s="85"/>
       <c r="W13" s="4" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="81"/>
-      <c r="B14" s="82"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="82"/>
-      <c r="G14" s="83" t="s">
+      <c r="A14" s="80"/>
+      <c r="B14" s="81"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="81"/>
+      <c r="G14" s="82" t="s">
         <v>166</v>
       </c>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="84">
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="83">
         <f>(H14*4)+(I14*5)+(J14*7)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="85" t="s">
+      <c r="M14" s="84" t="s">
         <v>167</v>
       </c>
-      <c r="N14" s="86"/>
+      <c r="N14" s="85"/>
     </row>
     <row r="15" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A15" s="81"/>
-      <c r="B15" s="82"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="82"/>
-      <c r="G15" s="83" t="s">
+      <c r="A15" s="80"/>
+      <c r="B15" s="81"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="81"/>
+      <c r="G15" s="82" t="s">
         <v>168</v>
       </c>
-      <c r="H15" s="81">
+      <c r="H15" s="80">
         <v>1</v>
       </c>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="84">
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="83">
         <f>(H15*3)+(I15*4)+(J15*6)</f>
         <v>3</v>
       </c>
-      <c r="M15" s="85" t="s">
+      <c r="M15" s="84" t="s">
         <v>169</v>
       </c>
-      <c r="N15" s="86"/>
+      <c r="N15" s="85"/>
     </row>
     <row r="16" spans="1:23" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="81"/>
-      <c r="B16" s="82"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="82"/>
-      <c r="G16" s="156" t="s">
+      <c r="A16" s="80"/>
+      <c r="B16" s="81"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="81"/>
+      <c r="G16" s="155" t="s">
         <v>170</v>
       </c>
-      <c r="H16" s="156"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="156"/>
-      <c r="K16" s="87">
+      <c r="H16" s="155"/>
+      <c r="I16" s="155"/>
+      <c r="J16" s="155"/>
+      <c r="K16" s="86">
         <f>SUM(K9,K10,K13,K14,K15)</f>
         <v>14</v>
       </c>
-      <c r="M16" s="85" t="s">
+      <c r="M16" s="84" t="s">
         <v>171</v>
       </c>
-      <c r="N16" s="86"/>
+      <c r="N16" s="85"/>
     </row>
     <row r="17" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A17" s="81"/>
-      <c r="B17" s="82"/>
-      <c r="D17" s="81"/>
-      <c r="E17" s="82"/>
-      <c r="M17" s="85" t="s">
+      <c r="A17" s="80"/>
+      <c r="B17" s="81"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="81"/>
+      <c r="M17" s="84" t="s">
         <v>172</v>
       </c>
-      <c r="N17" s="86"/>
+      <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A18" s="81"/>
-      <c r="B18" s="82"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="82"/>
-      <c r="M18" s="85" t="s">
+      <c r="A18" s="80"/>
+      <c r="B18" s="81"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="81"/>
+      <c r="M18" s="84" t="s">
         <v>173</v>
       </c>
-      <c r="N18" s="86"/>
+      <c r="N18" s="85"/>
     </row>
     <row r="19" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A19" s="81"/>
-      <c r="B19" s="82"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="82"/>
-      <c r="M19" s="85" t="s">
+      <c r="A19" s="80"/>
+      <c r="B19" s="81"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="81"/>
+      <c r="M19" s="84" t="s">
         <v>174</v>
       </c>
-      <c r="N19" s="86"/>
+      <c r="N19" s="85"/>
     </row>
     <row r="20" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="81"/>
-      <c r="B20" s="82"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="82"/>
-      <c r="M20" s="85" t="s">
+      <c r="A20" s="80"/>
+      <c r="B20" s="81"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="81"/>
+      <c r="M20" s="84" t="s">
         <v>175</v>
       </c>
-      <c r="N20" s="86"/>
+      <c r="N20" s="85"/>
     </row>
     <row r="21" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="M21" s="85" t="s">
+      <c r="M21" s="84" t="s">
         <v>176</v>
       </c>
-      <c r="N21" s="86"/>
+      <c r="N21" s="85"/>
     </row>
     <row r="22" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="M22" s="85" t="s">
+      <c r="M22" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="N22" s="86"/>
+      <c r="N22" s="85"/>
     </row>
     <row r="23" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="M23" s="88" t="s">
+      <c r="M23" s="87" t="s">
         <v>178</v>
       </c>
-      <c r="N23" s="89">
+      <c r="N23" s="88">
         <f>SUM(N9:N22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M24" s="88" t="s">
+      <c r="M24" s="87" t="s">
         <v>179</v>
       </c>
-      <c r="N24" s="87">
+      <c r="N24" s="86">
         <f>(N23*0.01)+0.65</f>
         <v>0.65</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M25" s="88" t="s">
+      <c r="M25" s="87" t="s">
         <v>180</v>
       </c>
-      <c r="N25" s="90">
+      <c r="N25" s="89">
         <f>K16*N24</f>
         <v>9.1</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M26" s="88" t="s">
+      <c r="M26" s="87" t="s">
         <v>181</v>
       </c>
-      <c r="N26" s="91">
+      <c r="N26" s="90">
         <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="M27" s="92" t="s">
+      <c r="M27" s="91" t="s">
         <v>182</v>
       </c>
-      <c r="N27" s="93">
+      <c r="N27" s="92">
         <f>N25*N26</f>
         <v>172.9</v>
       </c>
@@ -11555,7 +11523,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" style="24" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" style="23" customWidth="1"/>
     <col min="3" max="3" width="12.69921875" style="1" customWidth="1"/>
     <col min="4" max="4" width="1.09765625" style="1" customWidth="1"/>
     <col min="5" max="5" width="24.8984375" style="1" customWidth="1"/>
@@ -11573,690 +11541,690 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="156" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157"/>
-      <c r="M1" s="157"/>
-      <c r="N1" s="157"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
     </row>
     <row r="2" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="163" t="s">
+      <c r="A3" s="162" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="163"/>
-      <c r="C3" s="163"/>
-      <c r="E3" s="163" t="s">
+      <c r="B3" s="162"/>
+      <c r="C3" s="162"/>
+      <c r="E3" s="162" t="s">
         <v>183</v>
       </c>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="163"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="163"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
+      <c r="M3" s="162"/>
+      <c r="N3" s="162"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="93" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="95">
+      <c r="B4" s="94">
         <f>'#Estimativa-APF#'!$N$27</f>
         <v>172.9</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="164" t="s">
+      <c r="E4" s="163" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="162" t="s">
+      <c r="F4" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="162"/>
-      <c r="H4" s="162" t="s">
+      <c r="G4" s="161"/>
+      <c r="H4" s="161" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="162"/>
-      <c r="J4" s="162" t="s">
+      <c r="I4" s="161"/>
+      <c r="J4" s="161" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="162"/>
-      <c r="L4" s="162" t="s">
+      <c r="K4" s="161"/>
+      <c r="L4" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="162"/>
-      <c r="N4" s="96"/>
+      <c r="M4" s="161"/>
+      <c r="N4" s="95"/>
     </row>
     <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>0</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="E5" s="164"/>
-      <c r="F5" s="162" t="s">
+      <c r="E5" s="163"/>
+      <c r="F5" s="161" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="162"/>
-      <c r="H5" s="162" t="s">
+      <c r="G5" s="161"/>
+      <c r="H5" s="161" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="162"/>
-      <c r="J5" s="162" t="s">
+      <c r="I5" s="161"/>
+      <c r="J5" s="161" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="162"/>
-      <c r="L5" s="162" t="s">
+      <c r="K5" s="161"/>
+      <c r="L5" s="161" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="162"/>
-      <c r="N5" s="40" t="s">
+      <c r="M5" s="161"/>
+      <c r="N5" s="39" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="96" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="98">
+      <c r="B6" s="97">
         <f>B4+(B4*B5)</f>
         <v>172.9</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="164"/>
-      <c r="F6" s="99">
+      <c r="E6" s="163"/>
+      <c r="F6" s="98">
         <f>B6*G6</f>
         <v>8.6450000000000014</v>
       </c>
-      <c r="G6" s="100">
+      <c r="G6" s="99">
         <v>0.05</v>
       </c>
-      <c r="H6" s="99">
+      <c r="H6" s="98">
         <f>B4*I6</f>
         <v>34.580000000000005</v>
       </c>
-      <c r="I6" s="100">
+      <c r="I6" s="99">
         <v>0.2</v>
       </c>
-      <c r="J6" s="99">
+      <c r="J6" s="98">
         <f>B4*K6</f>
         <v>112.38500000000001</v>
       </c>
-      <c r="K6" s="100">
+      <c r="K6" s="99">
         <v>0.65</v>
       </c>
-      <c r="L6" s="99">
+      <c r="L6" s="98">
         <f>B4*M6</f>
         <v>17.290000000000003</v>
       </c>
-      <c r="M6" s="100">
+      <c r="M6" s="99">
         <v>0.1</v>
       </c>
-      <c r="N6" s="99"/>
+      <c r="N6" s="98"/>
     </row>
     <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>1</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="E7" s="101" t="s">
+      <c r="C7" s="28"/>
+      <c r="E7" s="100" t="s">
         <v>190</v>
       </c>
-      <c r="F7" s="99">
+      <c r="F7" s="98">
         <f>F6*G7</f>
         <v>4.7547500000000014</v>
       </c>
-      <c r="G7" s="100">
+      <c r="G7" s="99">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H7" s="99">
+      <c r="H7" s="98">
         <f>H6*I7</f>
         <v>10.374000000000001</v>
       </c>
-      <c r="I7" s="100">
+      <c r="I7" s="99">
         <v>0.3</v>
       </c>
-      <c r="J7" s="99">
+      <c r="J7" s="98">
         <f>J6*K7</f>
         <v>13.4862</v>
       </c>
-      <c r="K7" s="100">
+      <c r="K7" s="99">
         <v>0.12</v>
       </c>
-      <c r="L7" s="99">
+      <c r="L7" s="98">
         <f>L6*M7</f>
         <v>0.86450000000000016</v>
       </c>
-      <c r="M7" s="100">
+      <c r="M7" s="99">
         <v>0.05</v>
       </c>
-      <c r="N7" s="102">
+      <c r="N7" s="101">
         <f>SUM(F7,H7,J7,L7)</f>
         <v>29.47945</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>40</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="E8" s="101" t="s">
+      <c r="E8" s="100" t="s">
         <v>193</v>
       </c>
-      <c r="F8" s="99">
+      <c r="F8" s="98">
         <f>F6*G8</f>
         <v>1.2967500000000001</v>
       </c>
-      <c r="G8" s="100">
+      <c r="G8" s="99">
         <v>0.15</v>
       </c>
-      <c r="H8" s="99">
+      <c r="H8" s="98">
         <f>H6*I8</f>
         <v>6.9160000000000013</v>
       </c>
-      <c r="I8" s="100">
+      <c r="I8" s="99">
         <v>0.2</v>
       </c>
-      <c r="J8" s="99">
+      <c r="J8" s="98">
         <f>J6*K8</f>
         <v>11.238500000000002</v>
       </c>
-      <c r="K8" s="100">
+      <c r="K8" s="99">
         <v>0.1</v>
       </c>
-      <c r="L8" s="99">
+      <c r="L8" s="98">
         <f>L6*M8</f>
         <v>0.86450000000000016</v>
       </c>
-      <c r="M8" s="100">
+      <c r="M8" s="99">
         <v>0.05</v>
       </c>
-      <c r="N8" s="102">
+      <c r="N8" s="101">
         <f>SUM(F8,H8,J8,L8)</f>
         <v>20.315750000000001</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <v>2</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="101" t="s">
+      <c r="E9" s="100" t="s">
         <v>195</v>
       </c>
-      <c r="F9" s="99">
+      <c r="F9" s="98">
         <f>F6*G9</f>
         <v>0.17290000000000003</v>
       </c>
-      <c r="G9" s="100">
+      <c r="G9" s="99">
         <v>0.02</v>
       </c>
-      <c r="H9" s="99">
+      <c r="H9" s="98">
         <f>H6*I9</f>
         <v>6.9160000000000013</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="99">
         <v>0.2</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="98">
         <f>J6*K9</f>
         <v>44.954000000000008</v>
       </c>
-      <c r="K9" s="100">
+      <c r="K9" s="99">
         <v>0.4</v>
       </c>
-      <c r="L9" s="99">
+      <c r="L9" s="98">
         <f>L6*M9</f>
         <v>2.5935000000000001</v>
       </c>
-      <c r="M9" s="100">
+      <c r="M9" s="99">
         <v>0.15</v>
       </c>
-      <c r="N9" s="102">
+      <c r="N9" s="101">
         <f>SUM(F9,H9,J9,L9)</f>
         <v>54.636400000000009</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="103" t="s">
+      <c r="A10" s="102" t="s">
         <v>196</v>
       </c>
-      <c r="B10" s="104">
+      <c r="B10" s="103">
         <f>(B7*B8)*B9</f>
         <v>80</v>
       </c>
-      <c r="C10" s="103" t="s">
+      <c r="C10" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="101" t="s">
+      <c r="E10" s="100" t="s">
         <v>197</v>
       </c>
-      <c r="F10" s="99">
+      <c r="F10" s="98">
         <f>F6*G10</f>
         <v>0.43225000000000008</v>
       </c>
-      <c r="G10" s="100">
+      <c r="G10" s="99">
         <v>0.05</v>
       </c>
-      <c r="H10" s="99">
+      <c r="H10" s="98">
         <f>H6*I10</f>
         <v>2.7664000000000004</v>
       </c>
-      <c r="I10" s="100">
+      <c r="I10" s="99">
         <v>0.08</v>
       </c>
-      <c r="J10" s="99">
+      <c r="J10" s="98">
         <f>J6*K10</f>
         <v>11.238500000000002</v>
       </c>
-      <c r="K10" s="100">
+      <c r="K10" s="99">
         <v>0.1</v>
       </c>
-      <c r="L10" s="99">
+      <c r="L10" s="98">
         <f>L6*M10</f>
         <v>1.7290000000000003</v>
       </c>
-      <c r="M10" s="100">
+      <c r="M10" s="99">
         <v>0.1</v>
       </c>
-      <c r="N10" s="102">
+      <c r="N10" s="101">
         <f>SUM(F10,H10,J10,L10)</f>
         <v>16.166150000000002</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="94" t="s">
+      <c r="A11" s="93" t="s">
         <v>198</v>
       </c>
-      <c r="B11" s="105">
+      <c r="B11" s="104">
         <f>B6/B10*2</f>
         <v>4.3224999999999998</v>
       </c>
-      <c r="C11" s="94" t="s">
+      <c r="C11" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="101" t="s">
+      <c r="E11" s="100" t="s">
         <v>199</v>
       </c>
-      <c r="F11" s="99">
+      <c r="F11" s="98">
         <f>F6*G11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="100">
+      <c r="G11" s="99">
         <v>0</v>
       </c>
-      <c r="H11" s="99">
+      <c r="H11" s="98">
         <f>H6*I11</f>
         <v>0.6916000000000001</v>
       </c>
-      <c r="I11" s="100">
+      <c r="I11" s="99">
         <v>0.02</v>
       </c>
-      <c r="J11" s="99">
+      <c r="J11" s="98">
         <f>J6*K11</f>
         <v>5.619250000000001</v>
       </c>
-      <c r="K11" s="100">
+      <c r="K11" s="99">
         <v>0.05</v>
       </c>
-      <c r="L11" s="99">
+      <c r="L11" s="98">
         <f>L6*M11</f>
         <v>1.7290000000000003</v>
       </c>
-      <c r="M11" s="100">
+      <c r="M11" s="99">
         <v>0.1</v>
       </c>
-      <c r="N11" s="102">
+      <c r="N11" s="101">
         <f>SUM(F11,H11,J11,L11)</f>
         <v>8.0398500000000013</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="93" t="s">
         <v>200</v>
       </c>
-      <c r="B12" s="105">
+      <c r="B12" s="104">
         <f>B11/4</f>
         <v>1.0806249999999999</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="C12" s="93" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="106" t="s">
+      <c r="E12" s="105" t="s">
         <v>201</v>
       </c>
-      <c r="F12" s="107">
+      <c r="F12" s="106">
         <f t="shared" ref="F12:M12" si="0">SUM(F7:F11)</f>
         <v>6.6566500000000017</v>
       </c>
-      <c r="G12" s="108">
+      <c r="G12" s="107">
         <f t="shared" si="0"/>
         <v>0.77000000000000013</v>
       </c>
-      <c r="H12" s="107">
+      <c r="H12" s="106">
         <f t="shared" si="0"/>
         <v>27.664000000000005</v>
       </c>
-      <c r="I12" s="108">
+      <c r="I12" s="107">
         <f t="shared" si="0"/>
         <v>0.79999999999999993</v>
       </c>
-      <c r="J12" s="107">
+      <c r="J12" s="106">
         <f t="shared" si="0"/>
         <v>86.536450000000002</v>
       </c>
-      <c r="K12" s="108">
+      <c r="K12" s="107">
         <f t="shared" si="0"/>
         <v>0.77</v>
       </c>
-      <c r="L12" s="107">
+      <c r="L12" s="106">
         <f t="shared" si="0"/>
         <v>7.7805000000000009</v>
       </c>
-      <c r="M12" s="108">
+      <c r="M12" s="107">
         <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
-      <c r="N12" s="106"/>
+      <c r="N12" s="105"/>
     </row>
     <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="103" t="s">
+      <c r="A13" s="102" t="s">
         <v>202</v>
       </c>
-      <c r="B13" s="109">
+      <c r="B13" s="108">
         <f>B11/B9</f>
         <v>2.1612499999999999</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="E13" s="101" t="s">
+      <c r="E13" s="100" t="s">
         <v>204</v>
       </c>
-      <c r="F13" s="99">
+      <c r="F13" s="98">
         <f>F6*G13</f>
         <v>0.25935000000000002</v>
       </c>
-      <c r="G13" s="100">
+      <c r="G13" s="99">
         <v>0.03</v>
       </c>
-      <c r="H13" s="99">
+      <c r="H13" s="98">
         <f>H6*I13</f>
         <v>2.7664000000000004</v>
       </c>
-      <c r="I13" s="100">
+      <c r="I13" s="99">
         <v>0.08</v>
       </c>
-      <c r="J13" s="99">
+      <c r="J13" s="98">
         <f>J6*K13</f>
         <v>14.610050000000001</v>
       </c>
-      <c r="K13" s="100">
+      <c r="K13" s="99">
         <v>0.13</v>
       </c>
-      <c r="L13" s="99">
+      <c r="L13" s="98">
         <f>L6*M13</f>
         <v>5.1870000000000003</v>
       </c>
-      <c r="M13" s="100">
+      <c r="M13" s="99">
         <v>0.3</v>
       </c>
-      <c r="N13" s="102">
+      <c r="N13" s="101">
         <f>SUM(F13,H13,J13,L13)</f>
         <v>22.822800000000004</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E14" s="101" t="s">
+      <c r="E14" s="100" t="s">
         <v>205</v>
       </c>
-      <c r="F14" s="99">
+      <c r="F14" s="98">
         <f>F6*G14</f>
         <v>1.7290000000000003</v>
       </c>
-      <c r="G14" s="100">
+      <c r="G14" s="99">
         <v>0.2</v>
       </c>
-      <c r="H14" s="99">
+      <c r="H14" s="98">
         <f>H6*I14</f>
         <v>4.1496000000000004</v>
       </c>
-      <c r="I14" s="100">
+      <c r="I14" s="99">
         <v>0.12</v>
       </c>
-      <c r="J14" s="99">
+      <c r="J14" s="98">
         <f>J6*K14</f>
         <v>11.238500000000002</v>
       </c>
-      <c r="K14" s="100">
+      <c r="K14" s="99">
         <v>0.1</v>
       </c>
-      <c r="L14" s="99">
+      <c r="L14" s="98">
         <f>L6*M14</f>
         <v>4.3225000000000007</v>
       </c>
-      <c r="M14" s="100">
+      <c r="M14" s="99">
         <v>0.25</v>
       </c>
-      <c r="N14" s="102">
+      <c r="N14" s="101">
         <f>SUM(F14,H14,J14,L14)</f>
         <v>21.439600000000002</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="E15" s="106" t="s">
+      <c r="E15" s="105" t="s">
         <v>206</v>
       </c>
-      <c r="F15" s="107">
+      <c r="F15" s="106">
         <f t="shared" ref="F15:M15" si="1">SUM(F13:F14)</f>
         <v>1.9883500000000003</v>
       </c>
-      <c r="G15" s="108">
+      <c r="G15" s="107">
         <f t="shared" si="1"/>
         <v>0.23</v>
       </c>
-      <c r="H15" s="107">
+      <c r="H15" s="106">
         <f t="shared" si="1"/>
         <v>6.9160000000000004</v>
       </c>
-      <c r="I15" s="108">
+      <c r="I15" s="107">
         <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
-      <c r="J15" s="107">
+      <c r="J15" s="106">
         <f t="shared" si="1"/>
         <v>25.848550000000003</v>
       </c>
-      <c r="K15" s="108">
+      <c r="K15" s="107">
         <f t="shared" si="1"/>
         <v>0.23</v>
       </c>
-      <c r="L15" s="107">
+      <c r="L15" s="106">
         <f t="shared" si="1"/>
         <v>9.509500000000001</v>
       </c>
-      <c r="M15" s="108">
+      <c r="M15" s="107">
         <f t="shared" si="1"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="N15" s="106"/>
+      <c r="N15" s="105"/>
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="163" t="s">
+      <c r="A16" s="162" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="163"/>
-      <c r="C16" s="163"/>
-      <c r="E16" s="40" t="s">
+      <c r="B16" s="162"/>
+      <c r="C16" s="162"/>
+      <c r="E16" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="F16" s="110">
+      <c r="F16" s="109">
         <f t="shared" ref="F16:M16" si="2">F12+F15</f>
         <v>8.6450000000000014</v>
       </c>
-      <c r="G16" s="111">
+      <c r="G16" s="110">
         <f t="shared" si="2"/>
         <v>1.0000000000000002</v>
       </c>
-      <c r="H16" s="110">
+      <c r="H16" s="109">
         <f t="shared" si="2"/>
         <v>34.580000000000005</v>
       </c>
-      <c r="I16" s="111">
+      <c r="I16" s="110">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J16" s="110">
+      <c r="J16" s="109">
         <f t="shared" si="2"/>
         <v>112.38500000000001</v>
       </c>
-      <c r="K16" s="111">
+      <c r="K16" s="110">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L16" s="110">
+      <c r="L16" s="109">
         <f t="shared" si="2"/>
         <v>17.290000000000003</v>
       </c>
-      <c r="M16" s="111">
+      <c r="M16" s="110">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="112">
+      <c r="N16" s="111">
         <f>SUM(N7:N11,N13,N14)</f>
         <v>172.90000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="113">
+      <c r="B17" s="112">
         <v>20</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="N17" s="57"/>
+      <c r="C17" s="36"/>
+      <c r="N17" s="56"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="37">
         <f>B6*B17</f>
         <v>3458</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="L18" s="57"/>
-      <c r="N18" s="57"/>
+      <c r="C18" s="36"/>
+      <c r="L18" s="56"/>
+      <c r="N18" s="56"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="27">
         <v>0</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="N19" s="57"/>
+      <c r="C19" s="36"/>
+      <c r="N19" s="56"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="39">
+      <c r="B20" s="38">
         <f>B18*B19</f>
         <v>0</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="L20" s="57"/>
-      <c r="N20" s="57"/>
+      <c r="C20" s="36"/>
+      <c r="L20" s="56"/>
+      <c r="N20" s="56"/>
     </row>
     <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="B21" s="114">
+      <c r="B21" s="113">
         <f>B18+B20</f>
         <v>3458</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="N21" s="57"/>
+      <c r="C21" s="36"/>
+      <c r="N21" s="56"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <v>0.2</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="J22" s="57"/>
+      <c r="C22" s="36"/>
+      <c r="J22" s="56"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="42">
+      <c r="B23" s="41">
         <f>B21*B22</f>
         <v>691.6</v>
       </c>
-      <c r="C23" s="37"/>
+      <c r="C23" s="36"/>
     </row>
     <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="B24" s="114">
+      <c r="B24" s="113">
         <f>B21+B23</f>
         <v>4149.6000000000004</v>
       </c>
-      <c r="C24" s="37"/>
+      <c r="C24" s="36"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="J26" s="57"/>
+      <c r="J26" s="56"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="J27" s="57"/>
+      <c r="J27" s="56"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N28" s="57"/>
+      <c r="N28" s="56"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N29" s="57"/>
+      <c r="N29" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="13">
